--- a/Solent-Power-Client-Presentation-Workbook.xlsx
+++ b/Solent-Power-Client-Presentation-Workbook.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1 Keyword Universe'!$A$1:$H$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 Keyword-Page Map'!$A$1:$J$156</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3 Cannibalisation Summary'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3 Cannibalisation Summary'!$A$1:$E$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4 Redirects &amp; New Titles'!$A$1:$F$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5 Internal Links - Commercial'!$A$1:$D$236</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6 Internal Links - Blog'!$A$1:$D$191</definedName>
@@ -13224,13 +13224,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13246,12 +13247,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Pages involved</t>
+          <t>Affected URL</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>What to do</t>
+          <t>Role today</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
         </is>
       </c>
     </row>
@@ -13263,220 +13269,937 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>One buying intent (servicing/maintenance/contracts) spread over SIX pages. Google shows a different Solent page depending on the query — none of them well. 60,559 impressions in 90 days produced 27 clicks.</t>
+          <t>One buying intent (servicing / maintenance / contracts) spread over six pages — Google shows a different Solent page depending on the query, none of them well. 60,559 impressions in 90 days → 27 clicks.</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>/generator-service-maintenance/ (the rightful owner) · /how-often-should-generators-be-serviced/ (blog — currently WINS 'servicing and maintenance') · /knowledge-base/ (wins 'diesel generator maintenance') · /locations/surrey/ (wins 'generator service') · /hampshire-generators/ (wins 'repair near me') · /diesel-generator-service-contracts-uk-2026/</t>
+          <t>/generator-service-maintenance/</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>KEEP ALL PAGES — retitle so only the service page carries commercial servicing terms; blog keeps 'how often', locations keep '{service} {place}'. No redirects needed in this group.</t>
+          <t>The rightful owner — currently loses to the pages below</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>KEEP + REBUILD as the only page titled for servicing/maintenance/contracts terms (P1)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2 · UPS — two live trees</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>The UPS migration is HALF-DONE: /ups/* and /uninterruptible-power-supplies/* are both live with identical titles ('3 Phase UPS' twice, 'Modular UPS Systems' twice). The site competes with itself on every UPS category today.</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>/ups/three-phase/ vs /uninterruptible-power-supplies/three-phase-ups/ · /ups/modular/ vs …/modular/ · /ups/tower/ vs …/tower/ · /ups/configurable-output/ vs …/configurable-output/ · /ups/single-phase/ (new-tree home MISSING) · /ups/rack-mount/</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MERGE: 301 every old /ups/* URL to its new-tree twin; create /uninterruptible-power-supplies/single-phase-ups/ first. Then write unique descriptions (audit flags duplicates across UPS children).</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1 · Servicing &amp; maintenance</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>/how-often-should-generators-be-serviced/</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Blog post — currently WINS 'generator servicing and maintenance'</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>RETITLE to the question ('How often should a generator be serviced?'); link down to the service page with exact anchor</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>3 · kVA vs kW size series</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Two parallel size ladders (19 kVA + 21 kW pages) chase the same buyers. Google sometimes ranks the 25kVA page for '25kw generator' and vice versa. And 200kVA ≠ 200kW, so same-number pages actively mislead.</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>/generators/{N}kva/ ×19 live · /generators/{N}kw/ ×21 live</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MERGE (agreed): every kW page 301s ONCE to the kVA page covering its converted rating (kW÷0.8, round up). Full mapping + new titles/H1s on the Redirects tab. kW number goes into the kVA titles BEFORE redirecting.</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1 · Servicing &amp; maintenance</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>/knowledge-base/</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Hub page — currently wins 'diesel generator maintenance'</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Remove commercial servicing terms from title; becomes a pure guide index</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>4 · Products beating their own categories</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>For '30kva generator', '250 kva generator' etc., a single PRODUCT page outranks the category that should win — validated against the live SERPs, where competitors rank size CATEGORY pages.</t>
-        </is>
-      </c>
+          <t>1 · Servicing &amp; maintenance</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>e.g. /product/…/cps-ap30s-30kva…/ outranks /generators/30kva/ · same at 45/60/80/250/300kVA</t>
+          <t>/locations/surrey/</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>RETITLE products to their model terms ('CPS AP30S 30kVA Diesel Generator'); each product exact-anchor links UP to its size category. Categories get the merchandised titles (Redirects tab pattern).</t>
+          <t>Location page — currently wins national 'generator service'</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>RETITLE to 'Generator Servicing &amp; Repair in Surrey' — geo terms only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>5 · 'Commercial generator' — three owners</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Three different pages rank for 'commercial generator' depending on the day, including the hospital page.</t>
-        </is>
-      </c>
+          <t>1 · Servicing &amp; maintenance</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>/generators/industrial-generators/ · /hospital-generators/ · /generator-sales/emergency-generator-sales/</t>
+          <t>/hampshire-generators/</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>/generators/industrial-generators/ owns industrial + commercial (title covers both). Hospital page retitles to healthcare terms only.</t>
+          <t>Local hub — wins 'generator repair near me' family</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>KEEP those local/near-me terms — this page is doing its job; just stop it titling national terms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>6 · Brand pages — three URL patterns</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Most brands exist as a shop taxonomy page (/brand/), a content page (/brands/), and sometimes a sales page — splitting the brand's authority 2-3 ways. Three /brand/ pages are now 404 (teksan, cps, evopower).</t>
-        </is>
-      </c>
+          <t>1 · Servicing &amp; maintenance</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>/brand/{x}/ ×7 · /brands/{x}/ ×10 · /generator-sales/hyundai-generators/ etc. · 404s: /brand/teksan/, /brand/cps/, /brand/evopower/</t>
+          <t>/diesel-generator-service-contracts-uk-2026/</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ONE page per brand at /brands/{x}/. 301 the /brand/ taxonomy + sales duplicates in; fix the three 404s (301 to /brands/ twin or products).</t>
+          <t>New article overlapping the contracts intent</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Feed it: link prominently to the service page; don't let it title 'service contracts' commercially</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>7 · Sizing &amp; kVA guides</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Two sizing guides + a kVA-vs-kW explainer split the 'what size generator' demand; none rank top 3.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>/generator-sizing-specification/ · /what-size-generator-do-i-need/ · /the-differences-between-kva-and-kw/</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>MERGE the two sizing guides (301 what-size into sizing-specification). Keep kVA-vs-kW separate (different question) but rebuild with the conversion chart and links to every size page.</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2 · UPS — two live trees</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>The UPS migration is half-done: old and new category trees are BOTH live with identical titles. The site competes with itself on every UPS term today.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>/uninterruptible-power-supplies/</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>New hub — the keeper</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>KEEP — becomes the UPS hub; write unique descriptions for children</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>8 · Fuel services</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Fuel intent spread across two service pages, a blog and two hardware categories; 'fuel polishing' (300/mo, zero competition) has no owner.</t>
-        </is>
-      </c>
+          <t>2 · UPS — two live trees</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>/generator-fuel-services/ · /fuel-sampling-and-testing-services/ · /generator-fuel-types/ (blog) · /fuel-storage-tanks/ · /fuel-bowser/</t>
+          <t>/ups/three-phase/</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>/generator-fuel-services/ becomes the fuel hub with a fuel-polishing section (own child page later); sampling/testing stays but cross-linked as part of one offer; hardware categories unchanged.</t>
+          <t>Old twin of /uninterruptible-power-supplies/three-phase-ups/ (identical title '3 Phase UPS')</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>301 → /uninterruptible-power-supplies/three-phase-ups/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>9 · Contingency planning — new duplication</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>A new page shipped recently overlaps the existing contingency page — watch this doesn't become servicing 2.0.</t>
-        </is>
-      </c>
+          <t>2 · UPS — two live trees</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>/contingency-power-plan/ · /power-contingency-planning-30-days-uk/ (new)</t>
+          <t>/ups/modular/</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Differentiate now: contingency-power-plan = the service page; 30-days page = the campaign/guide, retitled and linking to it (or merge if content is 80% same).</t>
+          <t>Old twin — identical title 'Modular UPS Systems'</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>301 → /uninterruptible-power-supplies/modular/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>2 · UPS — two live trees</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>/ups/tower/</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Old twin — identical title 'Tower UPS'</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>301 → /uninterruptible-power-supplies/tower/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2 · UPS — two live trees</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>/ups/configurable-output/</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Old twin</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>301 → /uninterruptible-power-supplies/configurable-output/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2 · UPS — two live trees</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>/ups/single-phase/</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Old page whose new-tree home DOESN'T EXIST yet</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>CREATE /uninterruptible-power-supplies/single-phase-ups/ first, then 301 this into it</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2 · UPS — two live trees</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>/ups/rack-mount/</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Old page, no new-tree twin</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>CREATE or fold into the hub as a section, then 301</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2 · UPS — two live trees</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>/what-is-an-uninterruptible-power-supply/</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Blog — the site's best-ranking UPS URL today (pos 26-40)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Keeps the 'what is' question; links down to the hub with commercial anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>3 · kVA vs kW size series</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Two parallel size ladders (19 kVA + 21 kW pages) chase the same buyers, and 200kVA ≠ 200kW so same-number comparisons actively mislead. Client-agreed fix: one kVA-only ladder.</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>/generators/{N}kva/ — 19 live pages</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>The keepers</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Each gets the new title/H1 with its kW equivalent (see Redirects tab) BEFORE the kW redirects fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>3 · kVA vs kW size series</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>/generators/{N}kw/ — 21 live pages</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>The duplicates</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Each 301s ONCE to the kVA page covering its converted rating (kW ÷ 0.8, rounded up) — full per-page mapping on the Redirects tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>3 · kVA vs kW size series</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>/generators/1250kva/</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>404 right now (the live page is /generators/1250-kva/)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>301 the 404 to the hyphenated page immediately</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>4 · Products beating their own categories</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>For size searches like '30kva generator', a single product page outranks the category that should win — competitors win these SERPs with category pages.</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>/generators/30kva/</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Category — should own '30kva generator' but doesn't rank</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Merchandised title + intro; gains exact-anchor links from its products</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>4 · Products beating their own categories</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>/product/diesel-generators/cps-ap30s-30kva-diesel-generator/</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Product — currently ranks pos 7 for the size term</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>RETITLE to model term 'CPS AP30S 30kVA Diesel Generator'; link up to /generators/30kva/ with anchor '30kVA generators'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>4 · Products beating their own categories</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>(same pattern at 45 / 60 / 80 / 250 / 300kVA)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Product outranks or replaces category</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Same fix: product → model term, category → size term, exact-anchor link up</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>5 · 'Commercial generator' — three owners</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Three different pages rank for 'commercial generator' depending on the day, including the hospital page.</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>/generators/industrial-generators/</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Ranks pos 3-7 for industrial + commercial terms</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>THE owner — title covers 'Industrial &amp; Commercial Generators'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>5 · 'Commercial generator' — three owners</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>/hospital-generators/</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Currently pos 1 for 'commercial generator' (wrong job)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>RETITLE to healthcare terms only ('Hospital &amp; Healthcare Generators — HTM 06-01')</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>5 · 'Commercial generator' — three owners</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>/generator-sales/emergency-generator-sales/</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Also ranks for commercial/emergency generator</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Keeps 'emergency generator' (purchase intent) only</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>6 · Brand pages — three URL patterns</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Most brands exist as a shop taxonomy page (/brand/), a content page (/brands/), and sometimes a sales page — splitting each brand's authority 2-3 ways. Three /brand/ pages are now 404.</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>/brands/{brand}/ — 10 pages</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>The keepers (content + service pages)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Canonical pattern: one page per brand, sales + servicing together, dealer status in title</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>6 · Brand pages — three URL patterns</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>/brand/himoinsa/ · /brand/cat/ · /brand/pramac/ etc. (7 live)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Woo taxonomy duplicates</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>301 each into its /brands/ twin (or its category if no twin exists)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>6 · Brand pages — three URL patterns</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>/brand/teksan/ · /brand/cps/ · /brand/evopower/</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>404 right now</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>301 to the matching /brands/ page or the brand's product listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>6 · Brand pages — three URL patterns</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>/generator-sales/hyundai-generators/ · /generator-sales/teksan-generators/</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Third pattern — sales duplicates</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>301 into the /brands/ twin</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>6 · Brand pages — three URL patterns</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>/brand/hyundai/</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Currently noindexed (half-fix)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Replace noindex with a 301 when consolidation ships</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>7 · Sizing &amp; kVA guides</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Two sizing guides + a kVA-vs-kW explainer split the 'what size generator' demand; none rank top 3.</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>/generator-sizing-specification/</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>The keeper</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs the other guide; hosts the size chart; links to every size page (the ladder's link engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>7 · Sizing &amp; kVA guides</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>/what-size-generator-do-i-need/</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate sizing guide</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>301 → /generator-sizing-specification/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>7 · Sizing &amp; kVA guides</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>/the-differences-between-kva-and-kw/</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Separate question — keep</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>REBUILD with conversion chart (currently pos 34 for 'kva'); links to size ladder</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>8 · Fuel services</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Fuel intent spread across two service pages, a blog and hardware categories; 'fuel polishing' (300/mo, zero competition) has no owner.</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>/generator-fuel-services/</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>The keeper — becomes the fuel hub</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Add fuel polishing section (own child later) — 300/mo at KD 0 unowned</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>8 · Fuel services</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>/fuel-sampling-and-testing-services/</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Overlapping service page</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>KEEP but position as part of one fuel offer; heavy cross-links both ways</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>8 · Fuel services</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>/generator-fuel-types/</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Keeps informational fuel terms; links down to fuel services</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>8 · Fuel services</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>/fuel-storage-tanks/ · /fuel-bowser/ · /fuel-pods/</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Hardware categories</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Unchanged — link from the fuel hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>9 · Contingency planning — new duplication</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>A newly shipped page overlaps the existing contingency page — catch it before it becomes servicing 2.0.</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>/contingency-power-plan/</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Existing service page</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>THE owner of contingency/continuity planning terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>9 · Contingency planning — new duplication</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>/power-contingency-planning-30-days-uk/</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>New page (shipped recently)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Position as the campaign/guide ('30-day plan') linking to the service page — or merge if 80% same content</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>10 · BESS</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Two battery storage pages, one intent.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>/battery-energy-storage-solutions-bess/ · /battery-energy-storage-systems/</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Merge to one (keep the stronger URL, 301 the other). Low priority — the only high-difficulty cluster (KD 43).</t>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Two battery storage pages, one intent. Only high-difficulty cluster in the plan (KD 43) — low priority.</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>/battery-energy-storage-solutions-bess/</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Product category version</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Pick the stronger of the two as keeper</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>10 · BESS</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>/battery-energy-storage-systems/</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Service page version</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>301 the weaker into the keeper</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D11"/>
+  <autoFilter ref="A1:E40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Solent-Power-Client-Presentation-Workbook.xlsx
+++ b/Solent-Power-Client-Presentation-Workbook.xlsx
@@ -12,21 +12,23 @@
     <sheet name="2 Keyword-Page Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3 Cannibalisation Summary" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="4 Redirects &amp; New Titles" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5 Internal Links - Commercial" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6 Internal Links - Blog" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7 Power-Cut Checker Links" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="8 SEO Healthcheck" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="5 Quick Wins - Titles &amp; Metas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6 Internal Links - Commercial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7 Internal Links - Blog" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8 Power-Cut Checker Links" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9 SEO Healthcheck" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1 Keyword Universe'!$A$1:$H$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 Keyword-Page Map'!$A$1:$J$156</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3 Cannibalisation Summary'!$A$1:$E$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4 Redirects &amp; New Titles'!$A$1:$F$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5 Internal Links - Commercial'!$A$1:$D$236</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6 Internal Links - Blog'!$A$1:$D$191</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'7 Power-Cut Checker Links'!$A$1:$D$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'8 SEO Healthcheck'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4 Redirects &amp; New Titles'!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5 Quick Wins - Titles &amp; Metas'!$A$1:$I$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6 Internal Links - Commercial'!$A$1:$D$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'7 Internal Links - Blog'!$A$1:$D$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'8 Power-Cut Checker Links'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'9 SEO Healthcheck'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -54,7 +56,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +83,31 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -99,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -114,6 +141,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -481,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -556,72 +598,457 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The kW→kVA merge, one row per redirect, mapped by CONVERTED rating (kW ÷ 0.8, never same-number) with the new title + H1 for each target page — plus the UPS-tree completion and slug fixes. Titles go live BEFORE redirects fire.</t>
+          <t>The kW→kVA merge, one row per redirect, mapped by CONVERTED rating (kW ÷ 0.8, never same-number) with current→new H1, title and meta description for each target page — plus the UPS-tree completion and slug fixes. Titles go live BEFORE redirects fire. Current H1s/metas marked '(check CMS)' aren't externally retrievable (site blocks crawlers) — a SERanking pages export can backfill them.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>5 · Internal Links - Commercial</t>
+          <t>5 · Quick Wins - Titles &amp; Metas</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>One link per row: the page being edited, the link to add, the exact anchor text, and why. ~235 links. Also quietly fixes the audit's orphan-page warnings.</t>
+          <t>Every commercial page on one row: current → new H1, title and meta description, colour-coded by section (services / UPS / categories / size ladder / sectors / brands / local). This is the ship-this-week tab: pure title/H1/meta edits, no redirects, no content builds.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>6 · Internal Links - Blog</t>
+          <t>6 · Internal Links - Commercial</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1-2 links per blog post into commercial pages. Where we could retrieve the post's text, the exact existing sentence to hyperlink is quoted; otherwise anchor + placement is specified.</t>
+          <t>One link per row: the page being edited, the link to add, the exact anchor text, and why. ~235 links. Also quietly fixes the audit's orphan-page warnings.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>7 · Power-Cut Checker Links</t>
+          <t>7 · Internal Links - Blog</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>The checker is treated as a separate, protected asset: URLs frozen, no keyword changes — just one regionalised commercial callout per page.</t>
+          <t>1-2 links per blog post into commercial pages. Where we could retrieve the post's text, the exact existing sentence to hyperlink is quoted; otherwise anchor + placement is specified.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>8 · SEO Healthcheck</t>
+          <t>8 · Power-Cut Checker Links</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Technical fixes from the SERanking audit (03 Aug) + our crawl checks, priority-ordered. Site is healthy overall (84/100, CWV green) — the P1s are consolidation loose-ends.</t>
+          <t>The checker is treated as a separate, protected asset: URLs frozen, no keyword changes — just one regionalised commercial callout per page.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>9 · SEO Healthcheck</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Technical fixes from the SERanking audit (03 Aug) + our crawl checks, priority-ordered. Site is healthy overall (84/100, CWV green) — the P1s are consolidation loose-ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Sources</t>
         </is>
       </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Client GSC (3mo) · Ahrefs (Jul-Aug 2026) · SERanking audit 03-08-2026 · live SERP checks · Wayback copies for blog text. Site bot-protection blocked direct crawling; statuses cross-checked between SERanking and Ahrefs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate UPS trees both live</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>/ups/three-phase/, /ups/modular/, /ups/tower/, /ups/single-phase/, /ups/rack-mount/, /ups/configurable-output/ all return 200 alongside their /uninterruptible-power-supplies/ twins, with identical titles (verified in crawl data 2026-08).</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Complete the migration: create /uninterruptible-power-supplies/single-phase-ups/, then 301 every /ups/* URL to its new-tree twin. Until then the site cannibalises itself on every UPS term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>/generators/1250kva/ returns 404</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>SERanking 4XX list; the live page is /generators/1250-kva/ (hyphenated).</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>301 /generators/1250kva/ → /generators/1250-kva/. Check no other new large-size slugs 404.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>15 URLs return 4XX with internal links pointing at them</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Incl. /prevent-electrical-fire-thermographic-imaging/ (live twin exists at /thermographic-imaging/), /buy-diesel-generator/, /brand/teksan/, /brand/cps/, /brand/evopower/, /generators/doosan-generators/, /product/…/ap60s-60kva…/, + 5 dead blog posts (what-standby-generator-do-i-need, understanding-your-machinery-power-issues…, is-it-cheaper-to-run…, diesel-tax, portable-power-station posts).</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>301 each 404 to its nearest live equivalent (thermographic → /thermographic-imaging/; buy-diesel-generator → /diesel-generators/; /brand/ 404s → /brands/ twin or brand's products; dead posts → closest live guide) and update the internal links that point at them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Internal links point at 23 redirecting URLs</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Incl. /generator-servicing/, /generator-services/, /load-bank-testing/, /fuel-services/, /catalogue/, /standby-generators/, /uninterruptible-power-supply/, /ups/three-phase/, /ups/tower/, /ups/single-phase/, /generators/1500kva/, /generators/2000kva/, /generator-maintenance-checklist/, 3 long T&amp;C slugs, /product-category/diesel-generators/.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Update internal links (menus, footers, in-content) to point straight at the final URLs — every hop wastes equity and crawl budget. The good news: these redirects show the consolidation is already underway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>External links to 4XX on 540 pages</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>SERanking: a sitewide element (footer/template) links to at least one dead external URL — appears on 540 pages.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Find the dead external link in the shared template and fix once. One edit, 540 pages fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Mixed content on /agricultural-generators/</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>One asset (image/CSS/JS) loads over http://.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Swap the asset URL to https:// — one-line fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Titles too long on 234 pages</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SERanking; most will be replaced anyway by the new title patterns in this plan (services, categories, sizes, products).</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Apply the new title templates from the Redirects + linking tabs; keep ≤60 characters; for pages not covered by the plan, trim trailing boilerplate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate meta descriptions (5 groups) &amp; 35 too long</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Duplicates include the UPS children (both trees sharing descriptions), T&amp;C children, power-cut regional pages.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Unique 150-160 char descriptions for the UPS children when the trees merge; T&amp;C pages can share (or noindex); regional checker pages get one templated-but-regionalised description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>36 orphan pages, 25 pages with a single inbound link</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>One-inbound list = all 16 /locations/ pages, 8 /brands/ pages, /generators/1250-kva/, /generators/900kw/, several products.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Fixed by the two internal-linking tabs: brands block on the servicing page, coverage block on /hampshire-generators/, ladder links on size pages. No separate work needed — ship the linking tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Client GSC (3mo) · Ahrefs (Jul-Aug 2026) · SERanking audit 03-08-2026 · live SERP checks · Wayback copies for blog text. Site bot-protection blocked direct crawling; statuses cross-checked between SERanking and Ahrefs.</t>
+          <t>Multiple H1 tags on 2 pages + template check</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>SERanking flags 2; worth checking the blog/product templates that generate them.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>One H1 per page; demote extras to H2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>noindex on /brand/hyundai/ and knowledge-base pagination</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Part-finished brand cleanup; kb pagination noindex is fine.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>When brand consolidation ships, 301 /brand/hyundai/ into /brands/ twin instead of noindexing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Speed: 2 slow pages, JS unminified/uncached on 540, CSS uncompressed on 71</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Core Web Vitals are GREEN overall (desktop 90%+ good, mobile 83%+) — this is polish, not emergency.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Dev ticket: enable minification/caching in the optimisation plugin; re-test the 2 slow product pages after.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>staging2.solentpower.co.uk live &amp; crawlable</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Serves 200s (noindexed via x-robots).</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Password-protect staging. Zero-risk hygiene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Robots-blocked filter URLs (11) &amp; sitemap noindex header</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Filter/parameter URLs blocked in robots.txt; sitemap_index.xml sends x-robots noindex.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Both are fine/intentional — no action. Listed so nobody 'fixes' them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Overall health</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>SERanking score 84/100, Core Web Vitals green, 53 errors / 884 warnings, 537 of 594 crawled pages indexable.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>The site is technically healthy. The problems are structural (duplication + targeting), which is exactly what this plan addresses. No penalty signature anywhere.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
+  <autoFilter ref="A1:D16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14210,15 +14637,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14229,7 +14660,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Redirect TO</t>
+          <t>Redirect TO (target page)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -14239,7 +14670,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>New title for target page</t>
+          <t>Current H1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -14248,6 +14679,26 @@
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Current title</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>New title</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Current meta description</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>New meta description</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Before you redirect</t>
         </is>
@@ -14271,15 +14722,35 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>20kVA Diesel Generators (16kW)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>20kVA Diesel Generators For Sale in the UK | Solent Power UK</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>20kVA Diesel Generators (16kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>20kVA Diesel Generators (16kW)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Compare 20kVA diesel generators (16kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '10kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (16kW rated; suits 10kW requirements).</t>
         </is>
@@ -14303,15 +14774,35 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>20kVA Diesel Generators (16kW)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>20kVA Diesel Generators For Sale in the UK | Solent Power UK</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>20kVA Diesel Generators (16kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>20kVA Diesel Generators (16kW)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Compare 20kVA diesel generators (16kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '15kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (16kW rated; suits 15kW requirements).</t>
         </is>
@@ -14335,15 +14826,35 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25kVA Diesel Generators (20kW)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25kVA Diesel Generators (20kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25kVA Diesel Generators (20kW)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Compare 25kVA diesel generators (20kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '20kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (20kW rated; suits 20kW requirements).</t>
         </is>
@@ -14367,15 +14878,35 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40kVA Diesel Generators (32kW)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40kVA Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>40kVA Diesel Generators (32kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40kVA Diesel Generators (32kW)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Compare 40kVA diesel generators (32kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '25kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (32kW rated; suits 25kW requirements).</t>
         </is>
@@ -14399,15 +14930,35 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40kVA Diesel Generators (32kW)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40kVA Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>40kVA Diesel Generators (32kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>40kVA Diesel Generators (32kW)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Compare 40kVA diesel generators (32kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '30kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (32kW rated; suits 30kW requirements).</t>
         </is>
@@ -14431,15 +14982,35 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50kVA Diesel Generators (40kW)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50kVA Diesel Generators For Sale in the UK | Solent Power UK</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>50kVA Diesel Generators (40kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>50kVA Diesel Generators (40kW)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Compare 50kVA diesel generators (40kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '40kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (40kW rated; suits 40kW requirements).</t>
         </is>
@@ -14463,15 +15034,35 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>80kVA Diesel Generators (64kW)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>80kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>80kVA Diesel Generators (64kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>80kVA Diesel Generators (64kW)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Compare 80kVA diesel generators (64kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '50kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (64kW rated; suits 50kW requirements).</t>
         </is>
@@ -14495,15 +15086,35 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80kVA Diesel Generators (64kW)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>80kVA Diesel Generators (64kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>80kVA Diesel Generators (64kW)</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Compare 80kVA diesel generators (64kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '60kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (64kW rated; suits 60kW requirements).</t>
         </is>
@@ -14527,15 +15138,35 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100kVA Diesel Generators (80kW)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>100kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>100kVA Diesel Generators (80kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>100kVA Diesel Generators (80kW)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Compare 100kVA diesel generators (80kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '70kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (80kW rated; suits 70kW requirements).</t>
         </is>
@@ -14559,15 +15190,35 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>100kVA Diesel Generators (80kW)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>100kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>100kVA Diesel Generators (80kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>100kVA Diesel Generators (80kW)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Compare 100kVA diesel generators (80kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '80kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (80kW rated; suits 80kW requirements).</t>
         </is>
@@ -14591,15 +15242,35 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>150kVA Diesel Generators (120kW)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>150kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>150kVA Diesel Generators (120kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>150kVA Diesel Generators (120kW)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Compare 150kVA diesel generators (120kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '90kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (120kW rated; suits 90kW requirements).</t>
         </is>
@@ -14623,15 +15294,35 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>150kVA Diesel Generators (120kW)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>150kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>150kVA Diesel Generators (120kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>150kVA Diesel Generators (120kW)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Compare 150kVA diesel generators (120kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '100kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (120kW rated; suits 100kW requirements).</t>
         </is>
@@ -14655,15 +15346,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>200kVA Diesel Generators (160kW)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>200kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>200kVA Diesel Generators (160kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>200kVA Diesel Generators (160kW)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Compare 200kVA diesel generators (160kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '150kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (160kW rated; suits 150kW requirements).</t>
         </is>
@@ -14687,15 +15398,35 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>250kVA Diesel Generators (200kW)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>250kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>250kVA Diesel Generators (200kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>250kVA Diesel Generators (200kW)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Compare 250kVA diesel generators (200kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '200kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (200kW rated; suits 200kW requirements).</t>
         </is>
@@ -14719,15 +15450,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>400kVA Diesel Generators (320kW)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>400kVA Generators | Solent Power</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>400kVA Diesel Generators (320kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>400kVA Diesel Generators (320kW)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Compare 400kVA diesel generators (320kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '250kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (320kW rated; suits 250kW requirements).</t>
         </is>
@@ -14751,15 +15502,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>400kVA Diesel Generators (320kW)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>400kVA Generators | Solent Power</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>400kVA Diesel Generators (320kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>400kVA Diesel Generators (320kW)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Compare 400kVA diesel generators (320kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '300kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (320kW rated; suits 300kW requirements).</t>
         </is>
@@ -14783,15 +15554,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>500kVA Diesel Generators (400kW)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>500kVA Diesel Generators For Sale in the UK | Solent Power UK</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>500kVA Diesel Generators (400kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>500kVA Diesel Generators (400kW)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Compare 500kVA diesel generators (400kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '400kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (400kW rated; suits 400kW requirements).</t>
         </is>
@@ -14815,15 +15606,35 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>700kVA Diesel Generators (560kW)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>700 kVA Diesel Generators for Sale in the UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>700kVA Diesel Generators (560kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>700kVA Diesel Generators (560kW)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Compare 700kVA diesel generators (560kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '500kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (560kW rated; suits 500kW requirements).</t>
         </is>
@@ -14847,15 +15658,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>800kVA Diesel Generators (640kW)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>800 kVA Diesel Generators For Sale in the UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>800kVA Diesel Generators (640kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>800kVA Diesel Generators (640kW)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Compare 800kVA diesel generators (640kW) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '600kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (640kW rated; suits 600kW requirements).</t>
         </is>
@@ -14879,15 +15710,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1000kVA Diesel Generators (800kW / 1MVA)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1000 kVA Generators | Solent Power</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>1000kVA Diesel Generators (800kW / 1MVA) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1000kVA Diesel Generators (800kW / 1MVA)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Compare 1000kVA diesel generators (800kW / 1MVA) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '800kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (800kW rated; suits 800kW requirements).</t>
         </is>
@@ -14911,15 +15762,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1250kVA Diesel Generators (1000kW / 1.25MVA)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>1250kVA Diesel Generators (1000kW / 1.25MVA) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1250kVA Diesel Generators (1000kW / 1.25MVA)</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Compare 1250kVA diesel generators (1000kW / 1.25MVA) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>BEFORE redirecting: add '900kW' to the target page — title/H1 as shown, plus one intro line naming the kW ratings it covers (1000kW rated; suits 900kW requirements).</t>
         </is>
@@ -14943,15 +15814,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1250kVA Diesel Generators (1000kW / 1.25MVA)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>1250kVA Diesel Generators (1000kW / 1.25MVA) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1250kVA Diesel Generators (1000kW / 1.25MVA)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Compare 1250kVA diesel generators (1000kW / 1.25MVA) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>301 immediately; also add '1 megawatt / 1MW generator' phrasing to the page copy ('1 megawatt generator rental' = 150 searches/mo).</t>
         </is>
@@ -14975,15 +15866,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>same pattern</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>1500kVA Diesel Generators (1200kW / 1.5MVA) · 2000kVA Diesel Generators (1600kW / 2MVA)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>same pattern</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Compare 1500kVA diesel generators (1200kW / 1.5MVA) with UK stock and expert sizing help. Standby &amp; prime ratings, install &amp; servicing available.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Internal links only — no new redirects needed.</t>
         </is>
@@ -15007,15 +15918,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>350kVA Diesel Generators (280kW)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>350kVA Diesel Generators (280kW) | UK Stock | Solent Power</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>350kVA Diesel Generators (280kW)</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Client call: stocked or not?</t>
         </is>
@@ -15039,27 +15970,4239 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>(children keep their new-tree titles)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Complete the 301s old tree → new tree. Single-phase needs its new-tree home created: /uninterruptible-power-supplies/single-phase-ups/.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F26"/>
+  <autoFilter ref="A1:J26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I90"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Current H1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>New H1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Current title</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>New title</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Current meta description</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>New meta description</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Power Continuity Specialists — Generators, UPS &amp; Servicing</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Generator Sales, Installations &amp; Services | Solent Power</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Power Continuity Specialists | Generators, UPS &amp; Servicing | Solent Power</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Standby generators, UPS systems and servicing contracts for hospitals, data centres and industry. Design, install, maintain — across southern England.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>THE repositioning move: from genset shop to continuity specialist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>/generator-service-maintenance/</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Generator Servicing &amp; Maintenance Contracts</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Generator Servicing and Maintenance | Solent Power</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Generator Servicing &amp; Maintenance Contracts | Solent Power</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Planned generator servicing and maintenance contracts across the South. HTM 06-01 aware, 24/7 callout, load bank testing included. Get a contract quote.</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>P1 — the money page. Owns service/servicing/maintenance/contracts/company terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>/generator-installation/</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Generator Installation — Backup &amp; Standby Power Systems</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Generator Installation | Backup Generator Installation Service</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Generator Installation | Backup &amp; Standby Systems | Solent Power</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Commercial and standby generator installation: survey, groundworks, ATS, commissioning. One team from design to handover, across southern England.</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Owns ALL commercial installation variants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>/generator-load-bank-testing/</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Generator Load Bank Testing</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Generator Load Bank Testing | Solent Power</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Generator Load Bank Testing | Compliance Testing | Solent Power</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Annual load bank testing proves your standby generator performs when it matters. Compliance-ready reports from our own engineers. Book a test.</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Already pos 2 — defend, don't rewrite content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>/generator-fuel-services/</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Generator Fuel Management Services</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Generator Fuel Management Services | Solent Power</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Generator Fuel Management | Polishing, Testing &amp; Delivery | Solent Power</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Fuel polishing, sampling and testing, tank cleaning and delivery for standby generators. Keep stored diesel in spec and your generator ready.</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Add fuel polishing section — 300/mo unowned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>/fuel-sampling-and-testing-services/</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Fuel Sampling &amp; Testing Services</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Fuel Sampling &amp; Testing Services | Solent Power</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Fuel Sampling &amp; Testing | Diesel Contamination Analysis | Solent Power</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Laboratory fuel sampling and testing for stored diesel: water, diesel bug and particulates found before they stop your generator.</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>/generator-hire/</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Industrial &amp; Commercial Generator Hire (20kVA-2000kVA)</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Industrial Generator Hire | Our Services | Solent Power UK</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Industrial Generator Hire | 20kVA-2000kVA | Solent Power</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Industrial generator hire across Hampshire and the South: 20kVA to 2MVA, delivered, installed and fuelled. Emergency hire available 24/7.</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Qualified + local hire terms only — never the bare national term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>/generator-sales/</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Generator Sales — 10kVA to 2500kVA</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Generator Sales ¬ Diesel Generators for Sale | Solent Power</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Generator Sales | Diesel Generators 10kVA-2500kVA | Solent Power</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>New, used and ex-hire diesel generators from 10kVA to 2.5MVA with expert sizing, delivery and installation. Talk to a specialist, not a catalogue.</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Note the '¬' typo in the current title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>/thermographic-imaging/</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Thermographic Imaging Surveys</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Thermographic Imaging | Solent Power</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Thermographic Imaging Surveys | Electrical Fault Detection | Solent Power</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Thermographic surveys catch overheating connections before they become failures or fires. Add a survey to your generator maintenance visit.</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>/contingency-power-plan/</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Power Contingency Planning for Business</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Contingency Power Plan | Solent Power UK</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Power Contingency Planning | Business Continuity Power | Solent Power</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>A tested contingency power plan for your site: risk assessment, standby generation, UPS and fuel strategy — before the next outage, not after.</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Owner of contingency/continuity terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>/power-contingency-planning-30-days-uk/</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Your Power Contingency Plan — Ready in 30 Days</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Power Contingency Planning in 30 Days (UK) | Solent Power</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Power Contingency Plan in 30 Days | The Process | Solent Power</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>How we take a UK site from assessment to a tested power contingency plan in 30 days: survey, temporary cover, testing and sign-off.</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Campaign/guide page — links to (not competes with) the service page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>/uninterruptible-power-supply-services/</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>UPS Services — Maintenance, Installation &amp; Batteries</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Uninterruptible Power Supply (UPS) Services | Solent Power</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>UPS Services | Maintenance, Installation &amp; Batteries | Solent Power</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Every UPS service in one place: maintenance contracts, installation and commissioning, battery testing and replacement. All major brands.</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>/ups-servicing-maintenance-repairs-uk/</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>UPS Servicing &amp; Maintenance Contracts</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>UPS Servicing UK: Battery Testing, SLAs &amp; Costs | Solent Power</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>UPS Servicing &amp; Maintenance Contracts | UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>UPS maintenance contracts with battery testing, defined SLAs and emergency response. Single and three phase, all major brands, UK-wide.</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Mirrors the generator retainer model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>/ups-installation-commissioning-southampton-hampshire/</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>UPS Installation &amp; Commissioning</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>UPS Installation &amp; Commissioning Southampton | BS EN 62040 Costs | Solent Power</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>UPS Installation &amp; Commissioning | BS EN 62040 | Solent Power</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>UPS installation and commissioning to BS EN 62040: site survey, electrical works, batteries and load testing. From single units to modular systems.</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Consider de-localising the slug's targeting — title now national.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>/generator-sales/standby-generators/</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Standby Generators — Sales &amp; Installation</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Standby Generator Sales | Backup Power for Business &amp; Homes</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Standby Generators | Sales &amp; Installation | Solent Power</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Standby generators sized, supplied and installed for businesses and homes. Automatic changeover, full servicing plans available.</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>/generator-sales/emergency-generator-sales/</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Emergency Generator Sales — Fast-Track Supply</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Emergency Generator Sales | Emergency Power Solutions</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Emergency Generator Sales | Fast-Track Supply &amp; Install | Solent Power</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Generator failed or project gone urgent? Fast-track supply and installation of standby generators, with hire cover while you wait.</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Purchase intent; hire intent goes to the hire page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>/generator-sales/manufacturing/</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Standby Power for Manufacturing</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Manufacturing Generator Sales | Standby &amp; Emergency Power</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Manufacturing Standby Power | Generators &amp; UPS | Solent Power</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Standby generators and UPS for manufacturing, including pharma and high-risk processes. Keep lines running through any grid failure.</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Sector page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>/uninterruptible-power-supplies/</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Uninterruptible Power Supplies (UPS) for Business</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Uninterruptible Power Supplies | Solent Power</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Uninterruptible Power Supplies | Industrial UPS Systems UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Industrial and commercial UPS from 1kVA to 900kVA: single and three phase, modular and online double conversion. Supplied, installed, maintained.</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>The UPS hub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>/uninterruptible-power-supplies/three-phase-ups/</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Three Phase UPS Systems (10-900kVA)</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>3 Phase UPS | Solent Power</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Three Phase UPS Systems | 10-900kVA | Solent Power</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Three phase UPS systems from 10kVA to 900kVA for server rooms, healthcare and industry. Titan and Taurus ranges with installation and maintenance.</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>/uninterruptible-power-supplies/single-phase-ups/</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Single Phase UPS Systems (1-10kVA)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Single Phase UPS Systems | 1-10kVA | Solent Power</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Single phase UPS from 1kVA to 10kVA: tower and rack-mount, online double conversion. Protect servers, comms and critical small loads.</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>CREATE this page, then 301 /ups/single-phase/ into it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>/uninterruptible-power-supplies/modular/</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Modular UPS Systems (15-900kVA)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Modular UPS Systems | Solent Power</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Modular UPS Systems | Scalable 15-900kVA | Solent Power</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Modular UPS that scales with your load: hot-swappable 15-900kVA, N+1 redundancy without oversizing. Specified, installed and maintained.</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>GSC shows demand with no rankings — quick win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>/uninterruptible-power-supplies/configurable-output/</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Configurable Output UPS Systems</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Configurable Output UPS Systems UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Configurable Output UPS | Bespoke Power Protection | Solent Power</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Configurable output UPS for non-standard voltages and loads. Bespoke power protection specified by our engineers.</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>/uninterruptible-power-supplies/tower/</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Tower UPS Systems</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Tower UPS | Solent Power</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Tower UPS Systems | Standalone UPS Units | Solent Power</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Standalone tower UPS units for offices, comms rooms and control systems. Online double conversion options from 1kVA.</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>/generators/</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Generators for Sale — by Size, Brand &amp; Application</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Top Generator Deals | Power Generators for Sale | Solent Power</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Generators for Sale | Browse by Size, Brand &amp; Type | Solent Power</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Browse diesel generators by kVA size, brand and application. UK stock, expert sizing and full installation and servicing available.</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Current title reads like a voucher site — the quickest tone fix on the site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>/diesel-generators/</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Diesel Generators for Sale in the UK</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Diesel Generators for Sale in the UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Diesel Generators for Sale UK | 10kVA-2500kVA Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Diesel generators from 10kVA to 2.5MVA: canopied, open-set and containerised, from CAT, Himoinsa, Pramac and more. Sizing help and UK delivery.</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>/generators/industrial-generators/</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Industrial &amp; Commercial Generators</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Industrial &amp; Commercial Generators | 20kVA-2.5MVA | Solent Power</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Industrial and commercial generators for factories, sites and critical facilities. 20kVA-2.5MVA with installation, fuel and maintenance.</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Single owner of industrial + commercial terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>/generators/silent-generators/</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Silent Generators</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Silent Generators for Sale | Canopied &amp; Acoustic | Solent Power</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Silent and super-silent canopied generators for noise-sensitive sites and events. Compare dB(A) levels across sizes; hire options available.</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>TP 1300 — worth the push.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>/used-diesel-generators/</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Used &amp; Ex-Hire Diesel Generators</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Used &amp; Ex-Hire Diesel Generators | Tested &amp; Warrantied | Solent Power</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Used and ex-hire diesel generators, load-tested with service history and warranty. Stock changes fast — check availability.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Ranks pos 5 — merchandise, don't rebuild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>/generators/three-phase-generators/</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Three Phase Generators (400V)</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Three Phase Generators | 400V Diesel Generators | Solent Power</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Three phase 400V diesel generators for commercial and industrial loads. All sizes; sizing help from our engineers.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>/generators/single-phase-generators/</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Single Phase Generators (230V)</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Single Phase Generators | 230V Diesel Generators | Solent Power</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Single phase 230V diesel generators for smaller commercial and domestic standby loads.</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>/generators/stage-v-generators/</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Stage V Generators</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Stage V Generators | Emissions-Compliant Diesel | Solent Power</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>EU Stage V emissions-compliant diesel generators for urban and regulated sites, including NRMM-zone projects.</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>/generator-accessories/</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Generator Accessories</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Generator Accessories | Solent Power</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Generator Accessories | ATS, Controllers &amp; Parts | Solent Power</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>ATS panels, controllers, changeover switches and generator parts — matched to your set by our engineers.</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>/generator-accessories/automatic-transfer-switches/</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Automatic Transfer Switches (ATS)</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Automatic Transfer Switches | Solent Power</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Automatic Transfer Switches | ATS Panels 20A-2000A | Solent Power</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Automatic transfer switches from 20A to 2000A, single and three phase, from ABB and Socomec. Installation available.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Category owns switch terms; products take amp/model terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>/generator-accessories/manual-transfer-switches/</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Manual Transfer Switches</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Manual Transfer Switches | Solent Power</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Manual Transfer Switches | Generator Changeover | Solent Power</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Manual generator changeover switches for homes and small commercial installs. UK stock with installation guides.</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>/fuel-storage-tanks/</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Fuel Storage Tanks</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Fuel Storage Tanks | Solent Power UK</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Fuel Storage Tanks | Bunded Diesel Tanks | Solent Power</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Bunded diesel storage tanks for generator installations, with fuel management and polishing services available.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>/fuel-bowser/</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Towable Fuel Bowsers</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Fuel Bowsers | Towable Diesel Bowsers | Solent Power</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Fuel Bowsers | Towable Diesel Bowsers 1000-2000L | Solent Power</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Road-towable diesel bowsers from 1000 to 2000 litres for site refuelling.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>/generators/residential-generators/</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Home Standby Generators</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Home Standby Generators | Whole-House Backup | Solent Power</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Whole-house standby generators with automatic changeover — power cuts handled without lifting a finger.</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Kept live but OUT of main nav per client decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>/generators/10kva/</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>10kVA Diesel Generators (8kW)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>10kVA Generators | Solent Power</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>10kVA Diesel Generators (8kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Compare 10kVA diesel generators (8kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab. (kept live, out of main nav per client decision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>/generators/20kva/</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>20kVA Diesel Generators (16kW)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>20kVA Diesel Generators For Sale in the UK | Solent Power UK</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>20kVA Diesel Generators (16kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Compare 20kVA diesel generators (16kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab. (kept live, out of main nav per client decision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>/generators/25kva/</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>25kVA Diesel Generators (20kW)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>25kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>25kVA Diesel Generators (20kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Compare 25kVA diesel generators (20kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab. (kept live, out of main nav per client decision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>/generators/30kva/</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>30kVA Diesel Generators (24kW)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>30kVA Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>30kVA Diesel Generators (24kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Compare 30kVA diesel generators (24kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab. (kept live, out of main nav per client decision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>/generators/40kva/</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>40kVA Diesel Generators (32kW)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>40kVA Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>40kVA Diesel Generators (32kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Compare 40kVA diesel generators (32kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>/generators/50kva/</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>50kVA Diesel Generators (40kW)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>50kVA Diesel Generators For Sale in the UK | Solent Power UK</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>50kVA Diesel Generators (40kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Compare 50kVA diesel generators (40kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>/generators/60kva/</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>60kVA Diesel Generators (48kW)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>60kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>60kVA Diesel Generators (48kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Compare 60kVA diesel generators (48kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>/generators/80kva/</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>80kVA Diesel Generators (64kW)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>80kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>80kVA Diesel Generators (64kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Compare 80kVA diesel generators (64kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>/generators/100kva/</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>100kVA Diesel Generators (80kW)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>100kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>100kVA Diesel Generators (80kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Compare 100kVA diesel generators (80kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>/generators/150kva/</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>150kVA Diesel Generators (120kW)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>150kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>150kVA Diesel Generators (120kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Compare 150kVA diesel generators (120kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>/generators/200kva/</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>200kVA Diesel Generators (160kW)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>200kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>200kVA Diesel Generators (160kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Compare 200kVA diesel generators (160kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>/generators/250kva/</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>250kVA Diesel Generators (200kW)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>250kVA Diesel Generators For Sale in the UK - Solent Power</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>250kVA Diesel Generators (200kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Compare 250kVA diesel generators (200kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>/generators/300kva/</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>300kVA Diesel Generators (240kW)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>300kVA Diesel Generators For Sale in the UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>300kVA Diesel Generators (240kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Compare 300kVA diesel generators (240kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>/generators/400kva/</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>400kVA Diesel Generators (320kW)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>400kVA Generators | Solent Power</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>400kVA Diesel Generators (320kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Compare 400kVA diesel generators (320kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>/generators/500kva/</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>500kVA Diesel Generators (400kW)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>500kVA Diesel Generators For Sale in the UK | Solent Power UK</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>500kVA Diesel Generators (400kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Compare 500kVA diesel generators (400kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>/generators/600kva/</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>600kVA Diesel Generators (480kW)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>600 kVA Diesel Generators for Sale in the UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>600kVA Diesel Generators (480kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Compare 600kVA diesel generators (480kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>/generators/700kva/</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>700kVA Diesel Generators (560kW)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>700 kVA Diesel Generators for Sale in the UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>700kVA Diesel Generators (560kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Compare 700kVA diesel generators (560kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>/generators/800kva/</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>800kVA Diesel Generators (640kW)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>800 kVA Diesel Generators For Sale in the UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>800kVA Diesel Generators (640kW) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Compare 800kVA diesel generators (640kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>/generators/1000kva/</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>1000kVA Diesel Generators (800kW / 1MVA)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>1000 kVA Generators | Solent Power</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>1000kVA Diesel Generators (800kW / 1MVA) | UK Stock | Solent Power</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Compare 1000kVA diesel generators (800kW) with UK stock and expert sizing help. Standby and prime ratings, install and servicing available.</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Absorbs its kW twin(s) via 301 — see Redirects tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>/generators/1250-kva/</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>1250kVA Diesel Generators (1000kW / 1.25MVA)</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>1250kVA Diesel Generators (1000kW / 1.25MVA) | Solent Power</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>1250kVA (1.25MVA) diesel generators for data centres, healthcare and industry. Containerised and open-set options, with full project delivery.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>New page — carries kW AND MVA equivalents. Include '1 megawatt / 1MW generator' phrasing in the copy — 150/mo hire demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>/generators/1500-kva/</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>1500kVA Diesel Generators (1200kW / 1.5MVA)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>1500kVA Diesel Generators (1200kW / 1.5MVA) | Solent Power</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>1500kVA (1.5MVA) diesel generators for data centres, healthcare and industry. Containerised and open-set options, with full project delivery.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>New page — carries kW AND MVA equivalents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Size ladder (kVA)</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>/generators/2000-kva/</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>2000kVA Diesel Generators (1600kW / 2MVA)</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>2000kVA Diesel Generators (1600kW / 2MVA) | Solent Power</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>2000kVA (2MVA) diesel generators for data centres, healthcare and industry. Containerised and open-set options, with full project delivery.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>New page — carries kW AND MVA equivalents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>/hospital-generators/</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Hospital &amp; Healthcare Generators (HTM 06-01)</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Hospital &amp; Healthcare Generators | HTM 06-01 | Solent Power</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Standby generators and UPS for hospitals, clinics and healthcare estates, specified against HTM 06-01. Servicing contracts with compliance reports.</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>STOPS targeting 'commercial generator' — healthcare only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>/construction-generators/</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Construction Site Generators</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Construction Generators for Sale in the UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Construction Site Generators | Sales &amp; Hire | Solent Power</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Site power for construction: Stage V compliant generators to buy or hire, with fuel management and transfer switching.</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>/agricultural-generators/</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Agricultural Generators</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Agricultural Generators for Sale in the UK | Solent Power</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Agricultural Generators | Farm Standby Power | Solent Power</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Standby power for farms and rural businesses: single and three phase generators with automatic start on mains failure.</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>Also fix the mixed-content asset on this page (healthcheck).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>/brands/agg-generators/</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>Agg — Sales, Servicing &amp; Parts</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>AGG Generators | Generator Brands | Solent Power</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Agg Generators | Sales, Servicing &amp; Parts | Solent Power</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>Agg generator sales, servicing, repairs and parts from an independent specialist. All models supported, contracts available.</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>One page per brand — /brand/ taxonomy twins 301 in (Cannibalisation tab group 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>/brands/broadcrown-generators/</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Broadcrown — Sales, Servicing &amp; Parts</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Broadcrown Generators | Supported Brands | Solent Power</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Broadcrown Generators | Sales, Servicing &amp; Parts | Solent Power</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>Broadcrown generator sales, servicing, repairs and parts from an independent specialist. All models supported, contracts available.</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>One page per brand — /brand/ taxonomy twins 301 in (Cannibalisation tab group 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>/brands/comap-generator-controllers/</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Comap controllers — Service &amp; Support</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>ComAp | Supported Brands | Solent Power</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Comap controllers | Service &amp; Support | Solent Power</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>Comap controllers generator sales, servicing, repairs and parts from an independent specialist. All models supported, contracts available.</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>One page per brand — /brand/ taxonomy twins 301 in (Cannibalisation tab group 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>/brands/dale-power-solutions/</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Dale Power Solutions — Sales, Servicing &amp; Parts</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Dale Power Solutions | Supported Brands | Solent Power</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Dale Power Solutions | Service &amp; Support | Solent Power</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>Dale Power Solutions generator sales, servicing, repairs and parts from an independent specialist. All models supported, contracts available.</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>One page per brand — /brand/ taxonomy twins 301 in (Cannibalisation tab group 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>/brands/deep-sea-electronics/</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Deep Sea Electronics — Sales, Servicing &amp; Parts</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Deep Sea Electronics - Installation, Repair and Services | Solent Power</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Deep Sea Electronics | Service &amp; Support | Solent Power</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>Deep Sea Electronics generator sales, servicing, repairs and parts from an independent specialist. All models supported, contracts available.</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>One page per brand — /brand/ taxonomy twins 301 in (Cannibalisation tab group 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>/brands/fg-wilson-diesel-generators/</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Fg Wilson — Sales, Servicing &amp; Parts</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>FG Wilson Diesel Generators | Supported Brands | Solent Power</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>Fg Wilson Generators | Sales, Servicing &amp; Parts | Solent Power</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>Fg Wilson generator sales, servicing, repairs and parts from an independent specialist. All models supported, contracts available.</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>One page per brand — /brand/ taxonomy twins 301 in (Cannibalisation tab group 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>/brands/himoinsa-diesel-generators/</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Himoinsa — Sales, Servicing &amp; Parts</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Himoinsa Diesel Generators | Supported Brands | Solent Power</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Himoinsa Generators | Sales, Servicing &amp; Parts | Solent Power</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>Himoinsa generator sales, servicing, repairs and parts from an independent specialist. All models supported, contracts available.</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>One page per brand — /brand/ taxonomy twins 301 in (Cannibalisation tab group 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>/brands/musgrave-diesel-generators/</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Musgrave — Sales, Servicing &amp; Parts</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Musgrave Diesel Generators | Supported Brands | Solent Power</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Musgrave Generators | Sales, Servicing &amp; Parts | Solent Power</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>Musgrave generator sales, servicing, repairs and parts from an independent specialist. All models supported, contracts available.</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>One page per brand — /brand/ taxonomy twins 301 in (Cannibalisation tab group 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>/brands/sdmo-generators/</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Sdmo — Sales, Servicing &amp; Parts</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>SDMO Generators | Supported Brands | Solent Power</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>Sdmo Generators | Sales, Servicing &amp; Parts | Solent Power</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>Sdmo generator sales, servicing, repairs and parts from an independent specialist. All models supported, contracts available.</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>One page per brand — /brand/ taxonomy twins 301 in (Cannibalisation tab group 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>/brands/turner-diesel-generators/</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Turner — Sales, Servicing &amp; Parts</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>Turner Diesel Generators | Supported Brands | Solent Power</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>Turner Generators | Sales, Servicing &amp; Parts | Solent Power</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>Turner generator sales, servicing, repairs and parts from an independent specialist. All models supported, contracts available.</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>One page per brand — /brand/ taxonomy twins 301 in (Cannibalisation tab group 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>/hampshire-generators/</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Generator Sales, Servicing, Hire &amp; Repair in Hampshire</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>Hampshire Generators | Sales, Servicing, Hire &amp; Repair | Solent Power</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>Hampshire's generator specialists: sales, servicing, repair and hire from our Rowlands Castle base. Local engineers, 24/7 callout.</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>Best local asset — keep everything it already wins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>/locations/basingstoke/</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Basingstoke</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Basingstoke | Solent Power</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Basingstoke. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>/locations/hook/</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Hook</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Hook | Solent Power</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Hook. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>/locations/reading/</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Reading</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Reading | Solent Power</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Reading. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>/locations/bournemouth/</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Bournemouth</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Bournemouth | Solent Power</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Bournemouth. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>/locations/brighton-and-hove/</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Brighton And Hove</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Brighton And Hove | Solent Power</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Brighton And Hove. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>/locations/portsmouth/</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Portsmouth</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Portsmouth | Solent Power</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Portsmouth. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>/locations/luton/</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Luton</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Luton | Solent Power</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Luton. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>/locations/oxford/</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Oxford</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Oxford | Solent Power</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Oxford. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>/locations/surrey/</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Surrey</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Surrey | Solent Power</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Surrey. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>/locations/berkshire/</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Berkshire</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Berkshire | Solent Power</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Berkshire. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>/locations/southampton/</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Southampton</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Southampton | Solent Power</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Southampton. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>/locations/dorset/</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Dorset</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Dorset | Solent Power</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Dorset. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>/locations/winchester/</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Winchester</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Winchester | Solent Power</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Winchester. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>/locations/west-sussex/</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in West Sussex</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in West Sussex | Solent Power</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in West Sussex. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>/locations/petersfield/</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in Petersfield</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in Petersfield | Solent Power</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in Petersfield. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>/locations/new-forest/</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Generator Services in New Forest</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>Generator Servicing, Repair &amp; Hire in New Forest | Solent Power</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>(check CMS)</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>Generator servicing, repair, installation and hire in New Forest. Local engineers, 24/7 emergency callout, maintenance contracts. Call 02381 550144.</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>Geo terms only — national terms belong to the service pages.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I90"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20268,7 +25411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24491,7 +29634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24752,377 +29895,4 @@
   <autoFilter ref="A1:D11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Issue</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Duplicate UPS trees both live</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>/ups/three-phase/, /ups/modular/, /ups/tower/, /ups/single-phase/, /ups/rack-mount/, /ups/configurable-output/ all return 200 alongside their /uninterruptible-power-supplies/ twins, with identical titles (verified in crawl data 2026-08).</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Complete the migration: create /uninterruptible-power-supplies/single-phase-ups/, then 301 every /ups/* URL to its new-tree twin. Until then the site cannibalises itself on every UPS term.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>/generators/1250kva/ returns 404</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>SERanking 4XX list; the live page is /generators/1250-kva/ (hyphenated).</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>301 /generators/1250kva/ → /generators/1250-kva/. Check no other new large-size slugs 404.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>15 URLs return 4XX with internal links pointing at them</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Incl. /prevent-electrical-fire-thermographic-imaging/ (live twin exists at /thermographic-imaging/), /buy-diesel-generator/, /brand/teksan/, /brand/cps/, /brand/evopower/, /generators/doosan-generators/, /product/…/ap60s-60kva…/, + 5 dead blog posts (what-standby-generator-do-i-need, understanding-your-machinery-power-issues…, is-it-cheaper-to-run…, diesel-tax, portable-power-station posts).</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>301 each 404 to its nearest live equivalent (thermographic → /thermographic-imaging/; buy-diesel-generator → /diesel-generators/; /brand/ 404s → /brands/ twin or brand's products; dead posts → closest live guide) and update the internal links that point at them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Internal links point at 23 redirecting URLs</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Incl. /generator-servicing/, /generator-services/, /load-bank-testing/, /fuel-services/, /catalogue/, /standby-generators/, /uninterruptible-power-supply/, /ups/three-phase/, /ups/tower/, /ups/single-phase/, /generators/1500kva/, /generators/2000kva/, /generator-maintenance-checklist/, 3 long T&amp;C slugs, /product-category/diesel-generators/.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Update internal links (menus, footers, in-content) to point straight at the final URLs — every hop wastes equity and crawl budget. The good news: these redirects show the consolidation is already underway.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>External links to 4XX on 540 pages</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>SERanking: a sitewide element (footer/template) links to at least one dead external URL — appears on 540 pages.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Find the dead external link in the shared template and fix once. One edit, 540 pages fixed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Mixed content on /agricultural-generators/</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>One asset (image/CSS/JS) loads over http://.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Swap the asset URL to https:// — one-line fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Titles too long on 234 pages</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>SERanking; most will be replaced anyway by the new title patterns in this plan (services, categories, sizes, products).</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Apply the new title templates from the Redirects + linking tabs; keep ≤60 characters; for pages not covered by the plan, trim trailing boilerplate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Duplicate meta descriptions (5 groups) &amp; 35 too long</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Duplicates include the UPS children (both trees sharing descriptions), T&amp;C children, power-cut regional pages.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Unique 150-160 char descriptions for the UPS children when the trees merge; T&amp;C pages can share (or noindex); regional checker pages get one templated-but-regionalised description.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>36 orphan pages, 25 pages with a single inbound link</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>One-inbound list = all 16 /locations/ pages, 8 /brands/ pages, /generators/1250-kva/, /generators/900kw/, several products.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Fixed by the two internal-linking tabs: brands block on the servicing page, coverage block on /hampshire-generators/, ladder links on size pages. No separate work needed — ship the linking tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Multiple H1 tags on 2 pages + template check</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>SERanking flags 2; worth checking the blog/product templates that generate them.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>One H1 per page; demote extras to H2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>noindex on /brand/hyundai/ and knowledge-base pagination</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Part-finished brand cleanup; kb pagination noindex is fine.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>When brand consolidation ships, 301 /brand/hyundai/ into /brands/ twin instead of noindexing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Speed: 2 slow pages, JS unminified/uncached on 540, CSS uncompressed on 71</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Core Web Vitals are GREEN overall (desktop 90%+ good, mobile 83%+) — this is polish, not emergency.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Dev ticket: enable minification/caching in the optimisation plugin; re-test the 2 slow product pages after.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>staging2.solentpower.co.uk live &amp; crawlable</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Serves 200s (noindexed via x-robots).</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Password-protect staging. Zero-risk hygiene.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Robots-blocked filter URLs (11) &amp; sitemap noindex header</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Filter/parameter URLs blocked in robots.txt; sitemap_index.xml sends x-robots noindex.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Both are fine/intentional — no action. Listed so nobody 'fixes' them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Overall health</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>SERanking score 84/100, Core Web Vitals green, 53 errors / 884 warnings, 537 of 594 crawled pages indexable.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>The site is technically healthy. The problems are structural (duplication + targeting), which is exactly what this plan addresses. No penalty signature anywhere.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D16"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>